--- a/Curs Oficial/sesiuni/s05/echipa_galben/Vanzari.xlsx
+++ b/Curs Oficial/sesiuni/s05/echipa_galben/Vanzari.xlsx
@@ -422,22 +422,6 @@
           <t>Export linii vanzari · WMS BuildMat</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -445,22 +429,6 @@
           <t>Include comenzi partial livrate</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -608,7 +576,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -669,13 +636,11 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>584</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>2</v>
       </c>
@@ -728,7 +693,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -789,7 +753,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -852,7 +815,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -913,7 +875,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -974,7 +935,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1035,7 +995,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1096,7 +1055,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1157,7 +1115,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1218,7 +1175,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1279,7 +1235,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1340,7 +1295,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1401,7 +1355,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1462,7 +1415,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1523,7 +1475,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1584,7 +1535,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1647,7 +1597,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1708,7 +1657,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1769,7 +1717,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1832,7 +1779,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1893,7 +1839,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1958,7 +1903,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2019,7 +1963,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2082,7 +2025,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2143,7 +2085,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2204,7 +2145,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2265,7 +2205,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2326,7 +2265,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2387,7 +2325,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2448,7 +2385,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2509,7 +2445,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2572,7 +2507,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2635,7 +2569,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2696,7 +2629,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2759,7 +2691,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2820,7 +2751,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2881,7 +2811,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2942,7 +2871,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3003,7 +2931,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3066,7 +2993,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3129,7 +3055,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3190,7 +3115,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3251,7 +3175,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3312,7 +3235,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3373,7 +3295,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3434,7 +3355,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3497,7 +3417,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3558,7 +3477,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3619,7 +3537,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3680,7 +3597,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3743,26 +3659,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3823,7 +3719,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3884,7 +3779,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3945,7 +3839,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4006,7 +3899,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4067,7 +3959,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4075,22 +3966,6 @@
           <t>SUBTOTAL ZILNIC</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4151,7 +4026,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4212,7 +4086,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4275,7 +4148,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4338,7 +4210,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4399,7 +4270,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4460,7 +4330,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4523,7 +4392,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4584,7 +4452,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4647,7 +4514,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4710,7 +4576,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4771,7 +4636,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4832,7 +4696,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4893,7 +4756,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4958,7 +4820,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5019,7 +4880,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5080,7 +4940,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5141,7 +5000,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5204,7 +5062,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5265,7 +5122,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5326,7 +5182,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5389,7 +5244,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5452,7 +5306,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5513,7 +5366,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5574,7 +5426,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5635,7 +5486,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5696,7 +5546,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5757,7 +5606,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5818,7 +5666,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5881,7 +5728,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5944,7 +5790,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6005,7 +5850,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6068,7 +5912,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6129,7 +5972,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6190,7 +6032,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6253,7 +6094,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6314,7 +6154,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6375,7 +6214,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6436,7 +6274,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6499,7 +6336,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6521,7 +6357,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>3,5 buc</t>
+          <t>9 buc</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6562,7 +6398,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6625,7 +6460,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6686,7 +6520,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6747,7 +6580,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6808,7 +6640,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6871,7 +6702,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6932,7 +6762,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6993,7 +6822,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7054,7 +6882,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -7115,7 +6942,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7176,7 +7002,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7237,7 +7062,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7300,7 +7124,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7363,7 +7186,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7424,7 +7246,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7485,7 +7306,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7546,7 +7366,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7607,7 +7426,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7670,7 +7488,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7731,7 +7548,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7792,7 +7608,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7855,7 +7670,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7918,7 +7732,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7981,7 +7794,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -8046,7 +7858,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -8107,7 +7918,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -8172,7 +7982,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8233,7 +8042,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8294,7 +8102,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8355,7 +8162,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8416,7 +8222,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8424,22 +8229,6 @@
           <t>Total linii export: 128</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
